--- a/Notes/2025/07-2025 NOTES/14-31 July 2025 NOTES/14-31 July 2025 File Documents.xlsx
+++ b/Notes/2025/07-2025 NOTES/14-31 July 2025 NOTES/14-31 July 2025 File Documents.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Shared\Working Copy\Notes\2025\07-2025 NOTES\14-31 July 2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Shared\Working Copy\Notes\2025\07-2025 NOTES\14-31 July 2025 NOTES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A22552-BCAC-4185-9F5E-5A9E001EDBE1}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2A3BE1-8B07-4D42-98AD-23925F25F555}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1380" windowWidth="20490" windowHeight="8940" tabRatio="855" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="855" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ER" sheetId="22" r:id="rId1"/>
@@ -2874,18 +2874,33 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2907,21 +2922,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2994,6 +2994,33 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3021,34 +3048,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3516,24 +3516,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I50"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="78" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" style="78" customWidth="1"/>
     <col min="2" max="3" width="16" style="78" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="78" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" style="78" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" style="78" customWidth="1"/>
-    <col min="7" max="7" width="24.7109375" style="78" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="78"/>
+    <col min="4" max="4" width="14.33203125" style="78" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" style="78" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" style="78" customWidth="1"/>
+    <col min="7" max="7" width="24.6640625" style="78" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="78"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" customHeight="1">
-      <c r="A1" s="275" t="s">
+      <c r="A1" s="282" t="s">
         <v>227</v>
       </c>
-      <c r="B1" s="275"/>
-      <c r="C1" s="275"/>
-      <c r="D1" s="275"/>
+      <c r="B1" s="282"/>
+      <c r="C1" s="282"/>
+      <c r="D1" s="282"/>
       <c r="E1" s="84"/>
       <c r="F1" s="84"/>
       <c r="G1" s="84"/>
@@ -3544,10 +3544,10 @@
       <c r="A2" s="81" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="281" t="s">
+      <c r="B2" s="286" t="s">
         <v>160</v>
       </c>
-      <c r="C2" s="282"/>
+      <c r="C2" s="287"/>
       <c r="D2" s="81" t="s">
         <v>130</v>
       </c>
@@ -3559,10 +3559,10 @@
       <c r="A3" s="133">
         <v>1</v>
       </c>
-      <c r="B3" s="279" t="s">
+      <c r="B3" s="284" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="280"/>
+      <c r="C3" s="285"/>
       <c r="D3" s="232">
         <v>1343892</v>
       </c>
@@ -3571,10 +3571,10 @@
       <c r="A4" s="133">
         <v>2</v>
       </c>
-      <c r="B4" s="279" t="s">
+      <c r="B4" s="284" t="s">
         <v>107</v>
       </c>
-      <c r="C4" s="280"/>
+      <c r="C4" s="285"/>
       <c r="D4" s="232">
         <v>111420</v>
       </c>
@@ -3583,10 +3583,10 @@
       <c r="A5" s="133">
         <v>3</v>
       </c>
-      <c r="B5" s="279" t="s">
+      <c r="B5" s="284" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="280"/>
+      <c r="C5" s="285"/>
       <c r="D5" s="232">
         <v>6400</v>
       </c>
@@ -3595,20 +3595,20 @@
       <c r="A6" s="133">
         <v>4</v>
       </c>
-      <c r="B6" s="279" t="s">
+      <c r="B6" s="284" t="s">
         <v>131</v>
       </c>
-      <c r="C6" s="280"/>
+      <c r="C6" s="285"/>
       <c r="D6" s="232">
         <v>15480</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="19.5">
-      <c r="A7" s="283" t="s">
+    <row r="7" spans="1:9" ht="19.2">
+      <c r="A7" s="288" t="s">
         <v>156</v>
       </c>
-      <c r="B7" s="284"/>
-      <c r="C7" s="285"/>
+      <c r="B7" s="289"/>
+      <c r="C7" s="290"/>
       <c r="D7" s="134">
         <f>SUM(D3:D6)</f>
         <v>1477192</v>
@@ -3620,7 +3620,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="19.5">
+    <row r="8" spans="1:9" ht="19.2">
       <c r="A8" s="247"/>
       <c r="B8" s="247"/>
       <c r="C8" s="247"/>
@@ -3628,7 +3628,7 @@
       <c r="F8" s="249"/>
       <c r="G8" s="250"/>
     </row>
-    <row r="9" spans="1:9" ht="20.25" thickBot="1">
+    <row r="9" spans="1:9" ht="19.8" thickBot="1">
       <c r="A9" s="131"/>
       <c r="B9" s="131"/>
       <c r="C9" s="131"/>
@@ -3636,7 +3636,7 @@
       <c r="F9" s="126"/>
       <c r="G9" s="127"/>
     </row>
-    <row r="10" spans="1:9" ht="49.5">
+    <row r="10" spans="1:9" ht="50.4">
       <c r="A10" s="244" t="s">
         <v>114</v>
       </c>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="G11" s="127"/>
     </row>
-    <row r="12" spans="1:9" ht="29.45" customHeight="1">
+    <row r="12" spans="1:9" ht="29.4" customHeight="1">
       <c r="A12" s="251">
         <v>1477192</v>
       </c>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="G12" s="127"/>
     </row>
-    <row r="13" spans="1:9" ht="19.5">
+    <row r="13" spans="1:9" ht="19.2">
       <c r="A13" s="131"/>
       <c r="B13" s="131"/>
       <c r="C13" s="131"/>
@@ -3709,7 +3709,7 @@
       <c r="F13" s="126"/>
       <c r="G13" s="127"/>
     </row>
-    <row r="14" spans="1:9" ht="19.5">
+    <row r="14" spans="1:9" ht="19.2">
       <c r="A14" s="131"/>
       <c r="B14" s="131"/>
       <c r="C14" s="131"/>
@@ -3717,7 +3717,7 @@
       <c r="F14" s="126"/>
       <c r="G14" s="127"/>
     </row>
-    <row r="15" spans="1:9" ht="19.5">
+    <row r="15" spans="1:9" ht="19.2">
       <c r="A15" s="131"/>
       <c r="B15" s="131"/>
       <c r="C15" s="131"/>
@@ -3725,7 +3725,7 @@
       <c r="F15" s="126"/>
       <c r="G15" s="127"/>
     </row>
-    <row r="16" spans="1:9" ht="19.5">
+    <row r="16" spans="1:9" ht="19.2">
       <c r="A16" s="131"/>
       <c r="B16" s="131"/>
       <c r="C16" s="131"/>
@@ -3733,7 +3733,7 @@
       <c r="F16" s="126"/>
       <c r="G16" s="127"/>
     </row>
-    <row r="17" spans="1:7" ht="19.5">
+    <row r="17" spans="1:7" ht="19.2">
       <c r="A17" s="131"/>
       <c r="B17" s="131"/>
       <c r="C17" s="131"/>
@@ -3756,12 +3756,12 @@
       <c r="D19" s="123"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="276" t="s">
+      <c r="A20" s="283" t="s">
         <v>140</v>
       </c>
-      <c r="B20" s="276"/>
-      <c r="C20" s="276"/>
-      <c r="D20" s="276"/>
+      <c r="B20" s="283"/>
+      <c r="C20" s="283"/>
+      <c r="D20" s="283"/>
       <c r="G20" s="135" t="s">
         <v>212</v>
       </c>
@@ -3882,12 +3882,12 @@
       <c r="D30" s="86"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="276" t="s">
+      <c r="A31" s="283" t="s">
         <v>141</v>
       </c>
-      <c r="B31" s="276"/>
-      <c r="C31" s="276"/>
-      <c r="D31" s="276"/>
+      <c r="B31" s="283"/>
+      <c r="C31" s="283"/>
+      <c r="D31" s="283"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="81" t="s">
@@ -4023,28 +4023,28 @@
       <c r="D43" s="86"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="286" t="s">
+      <c r="A44" s="277" t="s">
         <v>142</v>
       </c>
-      <c r="B44" s="286"/>
-      <c r="C44" s="286"/>
-      <c r="D44" s="286"/>
+      <c r="B44" s="277"/>
+      <c r="C44" s="277"/>
+      <c r="D44" s="277"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="287" t="s">
+      <c r="A45" s="278" t="s">
         <v>163</v>
       </c>
-      <c r="B45" s="288"/>
+      <c r="B45" s="279"/>
       <c r="C45" s="242"/>
       <c r="D45" s="114" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A46" s="289" t="s">
+      <c r="A46" s="280" t="s">
         <v>168</v>
       </c>
-      <c r="B46" s="290"/>
+      <c r="B46" s="281"/>
       <c r="C46" s="243"/>
       <c r="D46" s="89">
         <f>D29</f>
@@ -4052,10 +4052,10 @@
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="289" t="s">
+      <c r="A47" s="280" t="s">
         <v>169</v>
       </c>
-      <c r="B47" s="290"/>
+      <c r="B47" s="281"/>
       <c r="C47" s="243"/>
       <c r="D47" s="89">
         <f>D40</f>
@@ -4063,10 +4063,10 @@
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="277" t="s">
+      <c r="A48" s="275" t="s">
         <v>158</v>
       </c>
-      <c r="B48" s="278"/>
+      <c r="B48" s="276"/>
       <c r="C48" s="241"/>
       <c r="D48" s="90">
         <f>SUM(D46:D47)</f>
@@ -4074,10 +4074,10 @@
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="277" t="s">
+      <c r="A49" s="275" t="s">
         <v>159</v>
       </c>
-      <c r="B49" s="278"/>
+      <c r="B49" s="276"/>
       <c r="C49" s="241"/>
       <c r="D49" s="90">
         <f>ER!D7</f>
@@ -4085,10 +4085,10 @@
       </c>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="277" t="s">
+      <c r="A50" s="275" t="s">
         <v>144</v>
       </c>
-      <c r="B50" s="278"/>
+      <c r="B50" s="276"/>
       <c r="C50" s="241"/>
       <c r="D50" s="90">
         <f>D49-D48</f>
@@ -4103,12 +4103,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A48:B48"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A31:D31"/>
@@ -4119,6 +4113,12 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A48:B48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4128,22 +4128,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:M27"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="19.5"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="19.2"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="31" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="31" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" style="31" customWidth="1"/>
-    <col min="4" max="4" width="23.7109375" style="31" customWidth="1"/>
+    <col min="1" max="1" width="1.6640625" style="31" customWidth="1"/>
+    <col min="2" max="2" width="30.44140625" style="31" customWidth="1"/>
+    <col min="3" max="3" width="24.109375" style="31" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" style="31" customWidth="1"/>
     <col min="5" max="5" width="21" style="31" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" style="31" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" style="31" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" style="31" customWidth="1"/>
-    <col min="9" max="9" width="24.5703125" style="31" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" style="31" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="31"/>
+    <col min="6" max="6" width="17.6640625" style="31" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" style="31" customWidth="1"/>
+    <col min="8" max="8" width="19.5546875" style="31" customWidth="1"/>
+    <col min="9" max="9" width="24.5546875" style="31" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" style="31" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="21.75">
+    <row r="1" spans="2:13" ht="22.2">
       <c r="B1" s="51"/>
       <c r="C1" s="51"/>
       <c r="D1" s="51"/>
@@ -4152,7 +4152,7 @@
       <c r="G1" s="51"/>
       <c r="H1" s="51"/>
     </row>
-    <row r="2" spans="2:13" ht="21.75">
+    <row r="2" spans="2:13" ht="22.2">
       <c r="B2" s="51"/>
       <c r="C2" s="51"/>
       <c r="D2" s="51"/>
@@ -4161,10 +4161,10 @@
       <c r="G2" s="51"/>
       <c r="H2" s="51"/>
     </row>
-    <row r="3" spans="2:13" ht="21.75">
+    <row r="3" spans="2:13" ht="22.2">
       <c r="B3" s="69">
         <f ca="1">NOW()</f>
-        <v>45876.727772222221</v>
+        <v>45881.09304861111</v>
       </c>
       <c r="C3" s="51"/>
       <c r="D3" s="51"/>
@@ -4173,7 +4173,7 @@
       <c r="G3" s="51"/>
       <c r="H3" s="51"/>
     </row>
-    <row r="4" spans="2:13" ht="21.75">
+    <row r="4" spans="2:13" ht="22.2">
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
       <c r="D4" s="51"/>
@@ -4182,7 +4182,7 @@
       <c r="G4" s="51"/>
       <c r="H4" s="51"/>
     </row>
-    <row r="5" spans="2:13" ht="21.75">
+    <row r="5" spans="2:13" ht="22.2">
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5" s="51"/>
@@ -4191,25 +4191,25 @@
       <c r="G5" s="51"/>
       <c r="H5" s="51"/>
     </row>
-    <row r="6" spans="2:13" ht="21.75">
+    <row r="6" spans="2:13" ht="22.2">
       <c r="B6"/>
       <c r="C6"/>
       <c r="D6" s="51"/>
       <c r="E6" s="70"/>
       <c r="F6" s="50"/>
-      <c r="G6" s="275"/>
+      <c r="G6" s="282"/>
       <c r="H6" s="51"/>
     </row>
-    <row r="7" spans="2:13" ht="21.75">
+    <row r="7" spans="2:13" ht="22.2">
       <c r="B7"/>
       <c r="C7"/>
       <c r="D7" s="51"/>
       <c r="E7" s="71"/>
       <c r="F7" s="50"/>
-      <c r="G7" s="275"/>
+      <c r="G7" s="282"/>
       <c r="H7" s="51"/>
     </row>
-    <row r="8" spans="2:13" ht="21.75">
+    <row r="8" spans="2:13" ht="22.2">
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8" s="51"/>
@@ -4219,7 +4219,7 @@
       <c r="H8" s="51"/>
       <c r="M8" s="169"/>
     </row>
-    <row r="9" spans="2:13" ht="21.75">
+    <row r="9" spans="2:13" ht="22.2">
       <c r="B9" s="72"/>
       <c r="C9" s="72"/>
       <c r="D9" s="51"/>
@@ -4228,7 +4228,7 @@
       <c r="G9" s="51"/>
       <c r="H9" s="51"/>
     </row>
-    <row r="10" spans="2:13" ht="21.75">
+    <row r="10" spans="2:13" ht="22.2">
       <c r="B10" s="32" t="s">
         <v>101</v>
       </c>
@@ -4265,7 +4265,7 @@
       <c r="I11" s="74"/>
       <c r="J11" s="75"/>
     </row>
-    <row r="12" spans="2:13" ht="21.75">
+    <row r="12" spans="2:13" ht="22.2">
       <c r="B12" s="39" t="s">
         <v>348</v>
       </c>
@@ -4285,7 +4285,7 @@
       <c r="H12" s="45"/>
       <c r="I12" s="74"/>
     </row>
-    <row r="13" spans="2:13" ht="21.75">
+    <row r="13" spans="2:13" ht="22.2">
       <c r="B13" s="46" t="s">
         <v>106</v>
       </c>
@@ -4303,7 +4303,7 @@
       <c r="H13" s="50"/>
       <c r="I13" s="76"/>
     </row>
-    <row r="14" spans="2:13" ht="21.75">
+    <row r="14" spans="2:13" ht="22.2">
       <c r="B14" s="51"/>
       <c r="C14" s="51"/>
       <c r="D14" s="51"/>
@@ -4312,7 +4312,7 @@
       <c r="G14" s="51"/>
       <c r="H14" s="51"/>
     </row>
-    <row r="15" spans="2:13" ht="21.75">
+    <row r="15" spans="2:13" ht="22.2">
       <c r="B15" s="54" t="s">
         <v>107</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="16" spans="2:13" ht="21.75">
+    <row r="16" spans="2:13" ht="22.2">
       <c r="B16" s="215">
         <v>103405</v>
       </c>
@@ -4355,7 +4355,7 @@
         <v>-414965</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="21.75">
+    <row r="17" spans="2:8" ht="22.2">
       <c r="B17" s="60">
         <v>62995</v>
       </c>
@@ -4373,7 +4373,7 @@
       <c r="G17" s="292"/>
       <c r="H17" s="295"/>
     </row>
-    <row r="18" spans="2:8" ht="21.75">
+    <row r="18" spans="2:8" ht="22.2">
       <c r="B18" s="62">
         <f>SUM(B16:B17)</f>
         <v>166400</v>
@@ -4394,7 +4394,7 @@
       <c r="G18" s="293"/>
       <c r="H18" s="296"/>
     </row>
-    <row r="19" spans="2:8" ht="21.75">
+    <row r="19" spans="2:8" ht="22.2">
       <c r="B19" s="51"/>
       <c r="C19" s="51"/>
       <c r="D19" s="51"/>
@@ -4403,7 +4403,7 @@
       <c r="G19" s="51"/>
       <c r="H19" s="51"/>
     </row>
-    <row r="20" spans="2:8" ht="21.75">
+    <row r="20" spans="2:8" ht="22.2">
       <c r="B20" s="36" t="s">
         <v>114</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="21.75">
+    <row r="21" spans="2:8" ht="22.2">
       <c r="B21" s="59" t="s">
         <v>119</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="21.75">
+    <row r="22" spans="2:8" ht="22.2">
       <c r="B22" s="68">
         <f>SUM(B18:E18)</f>
         <v>2405760</v>
@@ -4546,28 +4546,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:T23"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="11" style="78" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" style="78" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="78" customWidth="1"/>
     <col min="3" max="3" width="6" style="78" customWidth="1"/>
-    <col min="4" max="4" width="5.140625" style="78" customWidth="1"/>
+    <col min="4" max="4" width="5.109375" style="78" customWidth="1"/>
     <col min="5" max="5" width="5" style="78" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" style="78" customWidth="1"/>
-    <col min="7" max="7" width="5.140625" style="78" customWidth="1"/>
-    <col min="8" max="8" width="5.42578125" style="78" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" style="78" customWidth="1"/>
+    <col min="6" max="6" width="4.5546875" style="78" customWidth="1"/>
+    <col min="7" max="7" width="5.109375" style="78" customWidth="1"/>
+    <col min="8" max="8" width="5.44140625" style="78" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" style="78" customWidth="1"/>
     <col min="10" max="10" width="6" style="78" customWidth="1"/>
-    <col min="11" max="11" width="5.42578125" style="78" customWidth="1"/>
-    <col min="12" max="12" width="5.28515625" style="78" customWidth="1"/>
+    <col min="11" max="11" width="5.44140625" style="78" customWidth="1"/>
+    <col min="12" max="12" width="5.33203125" style="78" customWidth="1"/>
     <col min="13" max="14" width="5" style="78" customWidth="1"/>
-    <col min="15" max="15" width="5.28515625" style="78" customWidth="1"/>
-    <col min="16" max="16" width="6.5703125" style="78" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="78" customWidth="1"/>
+    <col min="15" max="15" width="5.33203125" style="78" customWidth="1"/>
+    <col min="16" max="16" width="6.5546875" style="78" customWidth="1"/>
+    <col min="17" max="17" width="11.6640625" style="78" customWidth="1"/>
     <col min="18" max="18" width="5" style="78" customWidth="1"/>
-    <col min="19" max="19" width="24.140625" style="78" customWidth="1"/>
-    <col min="20" max="20" width="16.28515625" style="78" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="78"/>
+    <col min="19" max="19" width="24.109375" style="78" customWidth="1"/>
+    <col min="20" max="20" width="16.33203125" style="78" customWidth="1"/>
+    <col min="21" max="16384" width="9.109375" style="78"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="36.75" customHeight="1">
@@ -4591,7 +4591,7 @@
       <c r="P1" s="300"/>
       <c r="Q1" s="300"/>
     </row>
-    <row r="2" spans="1:20" ht="53.25" thickBot="1">
+    <row r="2" spans="1:20" ht="50.4" thickBot="1">
       <c r="A2" s="81" t="s">
         <v>145</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>39375</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="17.45" hidden="1" customHeight="1" thickBot="1">
+    <row r="10" spans="1:20" ht="17.399999999999999" hidden="1" customHeight="1" thickBot="1">
       <c r="A10" s="303"/>
       <c r="B10" s="100" t="s">
         <v>149</v>
@@ -4980,7 +4980,7 @@
         <v>103405</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="53.25">
+    <row r="15" spans="1:20" ht="49.8">
       <c r="A15" s="81" t="s">
         <v>145</v>
       </c>
@@ -5081,7 +5081,7 @@
         <v>14320</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="16.899999999999999" hidden="1" customHeight="1">
+    <row r="17" spans="1:20" ht="16.95" hidden="1" customHeight="1">
       <c r="A17" s="303"/>
       <c r="B17" s="100" t="s">
         <v>126</v>
@@ -5347,16 +5347,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E701F96-EBD8-4B38-8387-22FB98C8588D}">
   <dimension ref="A1:G51"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" style="86" customWidth="1"/>
-    <col min="2" max="2" width="37.28515625" style="263" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="263" customWidth="1"/>
+    <col min="1" max="1" width="8.5546875" style="86" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" style="263" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="263" customWidth="1"/>
     <col min="4" max="4" width="11" style="86" customWidth="1"/>
     <col min="5" max="5" width="9" style="86" customWidth="1"/>
     <col min="6" max="6" width="16" style="86" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" style="78" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="78"/>
+    <col min="7" max="7" width="13.88671875" style="78" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="78"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5382,7 +5382,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="33">
+    <row r="2" spans="1:7" ht="33.6">
       <c r="A2" s="79">
         <v>1</v>
       </c>
@@ -5402,7 +5402,7 @@
         <v>7840</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="66">
+    <row r="3" spans="1:7" ht="67.2">
       <c r="A3" s="79">
         <v>2</v>
       </c>
@@ -5462,7 +5462,7 @@
         <v>44830</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="33">
+    <row r="6" spans="1:7" ht="33.6">
       <c r="A6" s="79">
         <v>5</v>
       </c>
@@ -5502,7 +5502,7 @@
         <v>4520</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="33">
+    <row r="8" spans="1:7" ht="33.6">
       <c r="A8" s="79">
         <v>7</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>370954</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="33">
+    <row r="10" spans="1:7">
       <c r="A10" s="79">
         <v>9</v>
       </c>
@@ -5562,7 +5562,7 @@
         <v>56900</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="33">
+    <row r="11" spans="1:7" ht="33.6">
       <c r="A11" s="79"/>
       <c r="B11" s="95" t="s">
         <v>331</v>
@@ -5940,26 +5940,26 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:T198"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.42578125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="6.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" style="1" customWidth="1"/>
     <col min="11" max="11" width="6" style="1" customWidth="1"/>
-    <col min="12" max="12" width="6.85546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.7109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="6.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.109375" style="1" customWidth="1"/>
     <col min="16" max="16" width="11" style="27" customWidth="1"/>
-    <col min="17" max="17" width="9.28515625" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="17" width="9.33203125" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="20.25" customHeight="1">
@@ -6032,7 +6032,7 @@
         <v>51200</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="27">
+    <row r="4" spans="1:17" ht="28.8">
       <c r="A4" s="309"/>
       <c r="B4" s="9" t="s">
         <v>17</v>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="O12" s="28"/>
     </row>
-    <row r="13" spans="1:17" ht="15.75">
+    <row r="13" spans="1:17" ht="15">
       <c r="A13" s="111">
         <v>45847</v>
       </c>
@@ -6478,7 +6478,7 @@
       <c r="O13" s="28"/>
       <c r="P13" s="164"/>
     </row>
-    <row r="14" spans="1:17" ht="15.75">
+    <row r="14" spans="1:17" ht="15">
       <c r="A14" s="111">
         <v>45848</v>
       </c>
@@ -6525,7 +6525,7 @@
       <c r="O14" s="28"/>
       <c r="P14" s="164"/>
     </row>
-    <row r="15" spans="1:17" ht="15.75">
+    <row r="15" spans="1:17" ht="15">
       <c r="A15" s="111">
         <v>45849</v>
       </c>
@@ -6568,7 +6568,7 @@
       <c r="O15" s="28"/>
       <c r="P15" s="164"/>
     </row>
-    <row r="16" spans="1:17" ht="15.75">
+    <row r="16" spans="1:17" ht="15">
       <c r="A16" s="111">
         <v>45850</v>
       </c>
@@ -6611,7 +6611,7 @@
       <c r="O16" s="28"/>
       <c r="P16" s="164"/>
     </row>
-    <row r="17" spans="1:20" ht="15.75">
+    <row r="17" spans="1:20" ht="15">
       <c r="A17" s="111">
         <v>45851</v>
       </c>
@@ -6658,7 +6658,7 @@
       <c r="O17" s="28"/>
       <c r="P17" s="164"/>
     </row>
-    <row r="18" spans="1:20" ht="15.75">
+    <row r="18" spans="1:20" ht="15">
       <c r="B18" s="26"/>
       <c r="M18" s="136" t="s">
         <v>16</v>
@@ -6670,7 +6670,7 @@
       <c r="O18" s="25"/>
       <c r="P18" s="164"/>
     </row>
-    <row r="19" spans="1:20" ht="15.75">
+    <row r="19" spans="1:20" ht="15">
       <c r="B19" s="26"/>
       <c r="H19" s="23"/>
       <c r="I19" s="23"/>
@@ -6684,14 +6684,14 @@
       <c r="O19" s="160"/>
       <c r="P19" s="164"/>
     </row>
-    <row r="20" spans="1:20" ht="15.75">
+    <row r="20" spans="1:20" ht="15">
       <c r="B20" s="26"/>
       <c r="M20" s="24"/>
       <c r="N20" s="25"/>
       <c r="O20" s="25"/>
       <c r="P20" s="164"/>
     </row>
-    <row r="21" spans="1:20" ht="15.75">
+    <row r="21" spans="1:20" ht="15">
       <c r="A21" s="29"/>
       <c r="B21" s="29"/>
       <c r="C21" s="29"/>
@@ -6708,7 +6708,7 @@
       <c r="O21" s="25"/>
       <c r="P21" s="164"/>
     </row>
-    <row r="22" spans="1:20" ht="15.75">
+    <row r="22" spans="1:20" ht="15">
       <c r="A22" s="29"/>
       <c r="B22" s="29"/>
       <c r="C22" s="29"/>
@@ -6728,7 +6728,7 @@
       <c r="R22" s="29"/>
       <c r="S22" s="29"/>
     </row>
-    <row r="23" spans="1:20" ht="15.75">
+    <row r="23" spans="1:20" ht="15">
       <c r="A23" s="29"/>
       <c r="B23" s="29"/>
       <c r="C23" s="29"/>
@@ -6748,7 +6748,7 @@
       <c r="R23" s="29"/>
       <c r="S23" s="29"/>
     </row>
-    <row r="24" spans="1:20" ht="15.75">
+    <row r="24" spans="1:20" ht="15">
       <c r="A24" s="29"/>
       <c r="B24" s="29"/>
       <c r="C24" s="29"/>
@@ -6768,7 +6768,7 @@
       <c r="R24" s="29"/>
       <c r="S24" s="29"/>
     </row>
-    <row r="25" spans="1:20" ht="15.75">
+    <row r="25" spans="1:20" ht="15">
       <c r="A25" s="29"/>
       <c r="B25" s="29"/>
       <c r="C25" s="29"/>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="T26" s="167"/>
     </row>
-    <row r="27" spans="1:20" ht="27">
+    <row r="27" spans="1:20" ht="28.8">
       <c r="A27" s="314"/>
       <c r="B27" s="154" t="s">
         <v>17</v>
@@ -7655,7 +7655,7 @@
       </c>
       <c r="O45" s="23"/>
     </row>
-    <row r="46" spans="1:19" ht="27">
+    <row r="46" spans="1:19" ht="28.8">
       <c r="A46" s="309"/>
       <c r="B46" s="9" t="s">
         <v>17</v>
@@ -10697,23 +10697,23 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F571C5-36CF-43CB-BBC6-C75CF5614662}">
   <dimension ref="A1:N155"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="5.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.44140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="1" customWidth="1"/>
-    <col min="9" max="9" width="6.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.109375" style="1" customWidth="1"/>
     <col min="13" max="13" width="11" style="27" customWidth="1"/>
-    <col min="14" max="14" width="9.28515625" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="9.33203125" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20.25" customHeight="1">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="L12" s="28"/>
     </row>
-    <row r="13" spans="1:14" ht="15.75">
+    <row r="13" spans="1:14" ht="15">
       <c r="A13" s="238"/>
       <c r="B13" s="30">
         <v>16</v>
@@ -11149,7 +11149,7 @@
       <c r="L13" s="28"/>
       <c r="M13" s="164"/>
     </row>
-    <row r="14" spans="1:14" ht="15.75">
+    <row r="14" spans="1:14" ht="15">
       <c r="A14" s="238"/>
       <c r="B14" s="30">
         <v>0</v>
@@ -11188,7 +11188,7 @@
       <c r="L14" s="28"/>
       <c r="M14" s="164"/>
     </row>
-    <row r="15" spans="1:14" ht="15.75">
+    <row r="15" spans="1:14" ht="15">
       <c r="A15" s="238"/>
       <c r="B15" s="30">
         <v>14</v>
@@ -11207,7 +11207,7 @@
         <v>175</v>
       </c>
       <c r="G15" s="138">
-        <f>E15*F15</f>
+        <f t="shared" ref="G15:G20" si="4">E15*F15</f>
         <v>1575</v>
       </c>
       <c r="H15" s="30">
@@ -11227,7 +11227,7 @@
       <c r="L15" s="28"/>
       <c r="M15" s="164"/>
     </row>
-    <row r="16" spans="1:14" ht="15.75">
+    <row r="16" spans="1:14" ht="15">
       <c r="A16" s="238"/>
       <c r="B16" s="30">
         <v>0</v>
@@ -11246,7 +11246,7 @@
         <v>120</v>
       </c>
       <c r="G16" s="138">
-        <f>E16*F16</f>
+        <f t="shared" si="4"/>
         <v>360</v>
       </c>
       <c r="H16" s="30">
@@ -11266,7 +11266,7 @@
       <c r="L16" s="28"/>
       <c r="M16" s="164"/>
     </row>
-    <row r="17" spans="1:13" ht="15.75">
+    <row r="17" spans="1:13" ht="15">
       <c r="A17" s="238"/>
       <c r="B17" s="30">
         <v>23</v>
@@ -11285,7 +11285,7 @@
         <v>175</v>
       </c>
       <c r="G17" s="138">
-        <f>E17*F17</f>
+        <f t="shared" si="4"/>
         <v>2275</v>
       </c>
       <c r="H17" s="30">
@@ -11305,7 +11305,7 @@
       <c r="L17" s="28"/>
       <c r="M17" s="164"/>
     </row>
-    <row r="18" spans="1:13" ht="15.75">
+    <row r="18" spans="1:13" ht="15">
       <c r="A18" s="238"/>
       <c r="B18" s="30">
         <v>0</v>
@@ -11324,7 +11324,7 @@
         <v>120</v>
       </c>
       <c r="G18" s="138">
-        <f>E18*F18</f>
+        <f t="shared" si="4"/>
         <v>480</v>
       </c>
       <c r="H18" s="30">
@@ -11344,7 +11344,7 @@
       <c r="L18" s="28"/>
       <c r="M18" s="164"/>
     </row>
-    <row r="19" spans="1:13" ht="15.75">
+    <row r="19" spans="1:13" ht="15">
       <c r="A19" s="238"/>
       <c r="B19" s="30">
         <v>19</v>
@@ -11363,7 +11363,7 @@
         <v>175</v>
       </c>
       <c r="G19" s="138">
-        <f>E19*F19</f>
+        <f t="shared" si="4"/>
         <v>2800</v>
       </c>
       <c r="H19" s="30">
@@ -11383,7 +11383,7 @@
       <c r="L19" s="28"/>
       <c r="M19" s="164"/>
     </row>
-    <row r="20" spans="1:13" ht="15.75">
+    <row r="20" spans="1:13" ht="15">
       <c r="A20" s="238"/>
       <c r="B20" s="30">
         <v>0</v>
@@ -11392,7 +11392,7 @@
         <v>80</v>
       </c>
       <c r="D20" s="138">
-        <f t="shared" ref="D20:D21" si="4">B20*C20</f>
+        <f t="shared" ref="D20" si="5">B20*C20</f>
         <v>0</v>
       </c>
       <c r="E20" s="30">
@@ -11402,7 +11402,7 @@
         <v>120</v>
       </c>
       <c r="G20" s="138">
-        <f>E20*F20</f>
+        <f t="shared" si="4"/>
         <v>480</v>
       </c>
       <c r="H20" s="30">
@@ -11412,7 +11412,7 @@
         <v>120</v>
       </c>
       <c r="J20" s="138">
-        <f t="shared" ref="J20:J21" si="5">H20*I20</f>
+        <f t="shared" ref="J20" si="6">H20*I20</f>
         <v>0</v>
       </c>
       <c r="K20" s="239">
@@ -11422,7 +11422,7 @@
       <c r="L20" s="28"/>
       <c r="M20" s="164"/>
     </row>
-    <row r="21" spans="1:13" ht="15.75">
+    <row r="21" spans="1:13" ht="15">
       <c r="A21" s="238"/>
       <c r="B21" s="30"/>
       <c r="C21" s="16"/>
@@ -11440,7 +11440,7 @@
       <c r="L21" s="28"/>
       <c r="M21" s="164"/>
     </row>
-    <row r="22" spans="1:13" ht="15.75">
+    <row r="22" spans="1:13" ht="15">
       <c r="B22" s="26"/>
       <c r="J22" s="136" t="s">
         <v>16</v>
@@ -13325,143 +13325,143 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:BP138"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="0.140625" style="23" customWidth="1"/>
-    <col min="2" max="2" width="3.5703125" style="26" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="2.85546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="3.28515625" style="208" customWidth="1"/>
-    <col min="7" max="7" width="2.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="0.109375" style="23" customWidth="1"/>
+    <col min="2" max="2" width="3.5546875" style="26" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="2.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="3.33203125" style="208" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="3" style="208" customWidth="1"/>
-    <col min="9" max="9" width="2.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="3.28515625" style="208" customWidth="1"/>
+    <col min="9" max="9" width="2.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="3.33203125" style="208" customWidth="1"/>
     <col min="11" max="11" width="3" style="1" customWidth="1"/>
-    <col min="12" max="12" width="3.140625" style="208" customWidth="1"/>
-    <col min="13" max="13" width="2.5703125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="2.85546875" style="208" customWidth="1"/>
+    <col min="12" max="12" width="3.109375" style="208" customWidth="1"/>
+    <col min="13" max="13" width="2.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="2.88671875" style="208" customWidth="1"/>
     <col min="15" max="15" width="3" style="1" customWidth="1"/>
-    <col min="16" max="16" width="2.85546875" style="208" customWidth="1"/>
+    <col min="16" max="16" width="2.88671875" style="208" customWidth="1"/>
     <col min="17" max="17" width="3" style="1" customWidth="1"/>
-    <col min="18" max="18" width="3.140625" style="208" customWidth="1"/>
+    <col min="18" max="18" width="3.109375" style="208" customWidth="1"/>
     <col min="19" max="19" width="3" style="1" customWidth="1"/>
-    <col min="20" max="20" width="2.85546875" style="208" customWidth="1"/>
+    <col min="20" max="20" width="2.88671875" style="208" customWidth="1"/>
     <col min="21" max="21" width="3" style="1" customWidth="1"/>
-    <col min="22" max="22" width="2.85546875" style="208" customWidth="1"/>
+    <col min="22" max="22" width="2.88671875" style="208" customWidth="1"/>
     <col min="23" max="23" width="3" style="1" customWidth="1"/>
-    <col min="24" max="24" width="3.140625" style="208" customWidth="1"/>
+    <col min="24" max="24" width="3.109375" style="208" customWidth="1"/>
     <col min="25" max="25" width="3" style="1" customWidth="1"/>
-    <col min="26" max="26" width="2.85546875" style="208" customWidth="1"/>
+    <col min="26" max="26" width="2.88671875" style="208" customWidth="1"/>
     <col min="27" max="27" width="3" style="1" customWidth="1"/>
-    <col min="28" max="28" width="2.7109375" style="208" customWidth="1"/>
+    <col min="28" max="28" width="2.6640625" style="208" customWidth="1"/>
     <col min="29" max="29" width="3" style="1" customWidth="1"/>
-    <col min="30" max="30" width="2.85546875" style="208" customWidth="1"/>
-    <col min="31" max="31" width="2.5703125" style="1" customWidth="1"/>
-    <col min="32" max="32" width="3.140625" style="208" customWidth="1"/>
-    <col min="33" max="33" width="2.42578125" style="1" customWidth="1"/>
-    <col min="34" max="34" width="2.85546875" style="208" customWidth="1"/>
-    <col min="35" max="35" width="2.42578125" style="1" customWidth="1"/>
+    <col min="30" max="30" width="2.88671875" style="208" customWidth="1"/>
+    <col min="31" max="31" width="2.5546875" style="1" customWidth="1"/>
+    <col min="32" max="32" width="3.109375" style="208" customWidth="1"/>
+    <col min="33" max="33" width="2.44140625" style="1" customWidth="1"/>
+    <col min="34" max="34" width="2.88671875" style="208" customWidth="1"/>
+    <col min="35" max="35" width="2.44140625" style="1" customWidth="1"/>
     <col min="36" max="36" width="3" style="208" customWidth="1"/>
-    <col min="37" max="37" width="3.140625" style="1" customWidth="1"/>
+    <col min="37" max="37" width="3.109375" style="1" customWidth="1"/>
     <col min="38" max="38" width="3" style="208" customWidth="1"/>
-    <col min="39" max="39" width="3.28515625" style="1" customWidth="1"/>
-    <col min="40" max="40" width="3.140625" style="208" customWidth="1"/>
+    <col min="39" max="39" width="3.33203125" style="1" customWidth="1"/>
+    <col min="40" max="40" width="3.109375" style="208" customWidth="1"/>
     <col min="41" max="41" width="3" style="1" customWidth="1"/>
-    <col min="42" max="42" width="2.85546875" style="208" customWidth="1"/>
-    <col min="43" max="43" width="2.7109375" style="1" customWidth="1"/>
-    <col min="44" max="44" width="2.7109375" style="208" customWidth="1"/>
-    <col min="45" max="45" width="2.85546875" style="1" customWidth="1"/>
-    <col min="46" max="46" width="2.85546875" style="208" customWidth="1"/>
-    <col min="47" max="47" width="2.7109375" style="1" customWidth="1"/>
-    <col min="48" max="48" width="2.7109375" style="208" customWidth="1"/>
-    <col min="49" max="49" width="2.7109375" style="1" hidden="1" customWidth="1"/>
-    <col min="50" max="50" width="2.7109375" style="208" hidden="1" customWidth="1"/>
+    <col min="42" max="42" width="2.88671875" style="208" customWidth="1"/>
+    <col min="43" max="43" width="2.6640625" style="1" customWidth="1"/>
+    <col min="44" max="44" width="2.6640625" style="208" customWidth="1"/>
+    <col min="45" max="45" width="2.88671875" style="1" customWidth="1"/>
+    <col min="46" max="46" width="2.88671875" style="208" customWidth="1"/>
+    <col min="47" max="47" width="2.6640625" style="1" customWidth="1"/>
+    <col min="48" max="48" width="2.77734375" style="208" customWidth="1"/>
+    <col min="49" max="49" width="2.6640625" style="1" hidden="1" customWidth="1"/>
+    <col min="50" max="50" width="2.6640625" style="208" hidden="1" customWidth="1"/>
     <col min="51" max="51" width="3" style="1" hidden="1" customWidth="1"/>
-    <col min="52" max="52" width="3.28515625" style="208" hidden="1" customWidth="1"/>
-    <col min="53" max="53" width="3.28515625" style="1" hidden="1" customWidth="1"/>
-    <col min="54" max="54" width="3.28515625" style="208" hidden="1" customWidth="1"/>
-    <col min="55" max="55" width="2.85546875" style="1" hidden="1" customWidth="1"/>
-    <col min="56" max="56" width="3.28515625" style="208" hidden="1" customWidth="1"/>
-    <col min="57" max="57" width="3.28515625" style="1" hidden="1" customWidth="1"/>
-    <col min="58" max="58" width="3.42578125" style="208" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="3.33203125" style="208" hidden="1" customWidth="1"/>
+    <col min="53" max="53" width="3.33203125" style="1" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="3.33203125" style="208" hidden="1" customWidth="1"/>
+    <col min="55" max="55" width="2.88671875" style="1" hidden="1" customWidth="1"/>
+    <col min="56" max="56" width="3.33203125" style="208" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="3.33203125" style="1" hidden="1" customWidth="1"/>
+    <col min="58" max="58" width="3.44140625" style="208" hidden="1" customWidth="1"/>
     <col min="59" max="59" width="4" style="1" customWidth="1"/>
-    <col min="60" max="60" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="4.140625" style="1" customWidth="1"/>
-    <col min="62" max="62" width="3.85546875" style="1" customWidth="1"/>
-    <col min="63" max="63" width="5.85546875" style="1" customWidth="1"/>
-    <col min="64" max="64" width="12.5703125" style="1" customWidth="1"/>
-    <col min="65" max="16384" width="9.140625" style="1"/>
+    <col min="60" max="60" width="3.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="4.109375" style="1" customWidth="1"/>
+    <col min="62" max="62" width="3.88671875" style="1" customWidth="1"/>
+    <col min="63" max="63" width="5.88671875" style="1" customWidth="1"/>
+    <col min="64" max="64" width="12.5546875" style="1" customWidth="1"/>
+    <col min="65" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="1" spans="1:68" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A1" s="189"/>
       <c r="C1" s="141"/>
       <c r="D1" s="141"/>
-      <c r="E1" s="276" t="s">
+      <c r="E1" s="283" t="s">
         <v>310</v>
       </c>
-      <c r="F1" s="276"/>
-      <c r="G1" s="276"/>
-      <c r="H1" s="276"/>
-      <c r="I1" s="276"/>
-      <c r="J1" s="276"/>
-      <c r="K1" s="276"/>
-      <c r="L1" s="276"/>
-      <c r="M1" s="276"/>
-      <c r="N1" s="276"/>
-      <c r="O1" s="276"/>
-      <c r="P1" s="276"/>
-      <c r="Q1" s="276"/>
-      <c r="R1" s="276"/>
-      <c r="S1" s="276"/>
-      <c r="T1" s="276"/>
-      <c r="U1" s="276"/>
-      <c r="V1" s="276"/>
-      <c r="W1" s="276"/>
-      <c r="X1" s="276"/>
-      <c r="Y1" s="276"/>
-      <c r="Z1" s="276"/>
-      <c r="AA1" s="276"/>
-      <c r="AB1" s="276"/>
-      <c r="AC1" s="276"/>
-      <c r="AD1" s="276"/>
-      <c r="AE1" s="276"/>
-      <c r="AF1" s="276"/>
-      <c r="AG1" s="276"/>
-      <c r="AH1" s="276"/>
-      <c r="AI1" s="276"/>
-      <c r="AJ1" s="276"/>
-      <c r="AK1" s="276"/>
-      <c r="AL1" s="276"/>
-      <c r="AM1" s="276"/>
-      <c r="AN1" s="276"/>
-      <c r="AO1" s="276"/>
-      <c r="AP1" s="276"/>
-      <c r="AQ1" s="276"/>
-      <c r="AR1" s="276"/>
-      <c r="AS1" s="276"/>
-      <c r="AT1" s="276"/>
-      <c r="AU1" s="276"/>
-      <c r="AV1" s="276"/>
-      <c r="AW1" s="276"/>
-      <c r="AX1" s="276"/>
-      <c r="AY1" s="276"/>
-      <c r="AZ1" s="276"/>
-      <c r="BA1" s="276"/>
-      <c r="BB1" s="276"/>
-      <c r="BC1" s="276"/>
-      <c r="BD1" s="276"/>
-      <c r="BE1" s="276"/>
-      <c r="BF1" s="276"/>
-      <c r="BG1" s="276"/>
-      <c r="BH1" s="276"/>
-      <c r="BI1" s="276"/>
-      <c r="BJ1" s="276"/>
+      <c r="F1" s="283"/>
+      <c r="G1" s="283"/>
+      <c r="H1" s="283"/>
+      <c r="I1" s="283"/>
+      <c r="J1" s="283"/>
+      <c r="K1" s="283"/>
+      <c r="L1" s="283"/>
+      <c r="M1" s="283"/>
+      <c r="N1" s="283"/>
+      <c r="O1" s="283"/>
+      <c r="P1" s="283"/>
+      <c r="Q1" s="283"/>
+      <c r="R1" s="283"/>
+      <c r="S1" s="283"/>
+      <c r="T1" s="283"/>
+      <c r="U1" s="283"/>
+      <c r="V1" s="283"/>
+      <c r="W1" s="283"/>
+      <c r="X1" s="283"/>
+      <c r="Y1" s="283"/>
+      <c r="Z1" s="283"/>
+      <c r="AA1" s="283"/>
+      <c r="AB1" s="283"/>
+      <c r="AC1" s="283"/>
+      <c r="AD1" s="283"/>
+      <c r="AE1" s="283"/>
+      <c r="AF1" s="283"/>
+      <c r="AG1" s="283"/>
+      <c r="AH1" s="283"/>
+      <c r="AI1" s="283"/>
+      <c r="AJ1" s="283"/>
+      <c r="AK1" s="283"/>
+      <c r="AL1" s="283"/>
+      <c r="AM1" s="283"/>
+      <c r="AN1" s="283"/>
+      <c r="AO1" s="283"/>
+      <c r="AP1" s="283"/>
+      <c r="AQ1" s="283"/>
+      <c r="AR1" s="283"/>
+      <c r="AS1" s="283"/>
+      <c r="AT1" s="283"/>
+      <c r="AU1" s="283"/>
+      <c r="AV1" s="283"/>
+      <c r="AW1" s="283"/>
+      <c r="AX1" s="283"/>
+      <c r="AY1" s="283"/>
+      <c r="AZ1" s="283"/>
+      <c r="BA1" s="283"/>
+      <c r="BB1" s="283"/>
+      <c r="BC1" s="283"/>
+      <c r="BD1" s="283"/>
+      <c r="BE1" s="283"/>
+      <c r="BF1" s="283"/>
+      <c r="BG1" s="283"/>
+      <c r="BH1" s="283"/>
+      <c r="BI1" s="283"/>
+      <c r="BJ1" s="283"/>
       <c r="BK1" s="141"/>
       <c r="BN1" s="190">
         <f>BJ138</f>
@@ -13476,223 +13476,223 @@
         <v>616</v>
       </c>
     </row>
-    <row r="2" spans="1:68" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="2" spans="1:68" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A2" s="189" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="315" t="s">
+      <c r="B2" s="324" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="318" t="s">
+      <c r="C2" s="327" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="321" t="s">
+      <c r="D2" s="330" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="324" t="s">
+      <c r="E2" s="321" t="s">
         <v>311</v>
       </c>
-      <c r="F2" s="324"/>
-      <c r="G2" s="324"/>
-      <c r="H2" s="324"/>
-      <c r="I2" s="324"/>
-      <c r="J2" s="324"/>
-      <c r="K2" s="324"/>
-      <c r="L2" s="324"/>
-      <c r="M2" s="324"/>
-      <c r="N2" s="324"/>
-      <c r="O2" s="324"/>
-      <c r="P2" s="324"/>
-      <c r="Q2" s="324"/>
-      <c r="R2" s="324"/>
-      <c r="S2" s="324"/>
-      <c r="T2" s="324"/>
-      <c r="U2" s="324"/>
-      <c r="V2" s="324"/>
-      <c r="W2" s="324"/>
-      <c r="X2" s="324"/>
-      <c r="Y2" s="324"/>
-      <c r="Z2" s="324"/>
-      <c r="AA2" s="324"/>
-      <c r="AB2" s="324"/>
-      <c r="AC2" s="324"/>
-      <c r="AD2" s="324"/>
-      <c r="AE2" s="324"/>
-      <c r="AF2" s="324"/>
-      <c r="AG2" s="324"/>
-      <c r="AH2" s="324"/>
-      <c r="AI2" s="324"/>
-      <c r="AJ2" s="324"/>
-      <c r="AK2" s="324"/>
-      <c r="AL2" s="324"/>
-      <c r="AM2" s="324"/>
-      <c r="AN2" s="324"/>
-      <c r="AO2" s="325"/>
-      <c r="AP2" s="325"/>
-      <c r="AQ2" s="325"/>
-      <c r="AR2" s="325"/>
-      <c r="AS2" s="325"/>
-      <c r="AT2" s="325"/>
-      <c r="AU2" s="325"/>
-      <c r="AV2" s="325"/>
-      <c r="AW2" s="325"/>
-      <c r="AX2" s="325"/>
-      <c r="AY2" s="325"/>
-      <c r="AZ2" s="325"/>
-      <c r="BA2" s="325"/>
-      <c r="BB2" s="325"/>
-      <c r="BC2" s="325"/>
-      <c r="BD2" s="325"/>
-      <c r="BE2" s="325"/>
-      <c r="BF2" s="325"/>
-      <c r="BG2" s="326" t="s">
-        <v>1</v>
-      </c>
-      <c r="BH2" s="326"/>
-      <c r="BI2" s="324" t="s">
+      <c r="F2" s="321"/>
+      <c r="G2" s="321"/>
+      <c r="H2" s="321"/>
+      <c r="I2" s="321"/>
+      <c r="J2" s="321"/>
+      <c r="K2" s="321"/>
+      <c r="L2" s="321"/>
+      <c r="M2" s="321"/>
+      <c r="N2" s="321"/>
+      <c r="O2" s="321"/>
+      <c r="P2" s="321"/>
+      <c r="Q2" s="321"/>
+      <c r="R2" s="321"/>
+      <c r="S2" s="321"/>
+      <c r="T2" s="321"/>
+      <c r="U2" s="321"/>
+      <c r="V2" s="321"/>
+      <c r="W2" s="321"/>
+      <c r="X2" s="321"/>
+      <c r="Y2" s="321"/>
+      <c r="Z2" s="321"/>
+      <c r="AA2" s="321"/>
+      <c r="AB2" s="321"/>
+      <c r="AC2" s="321"/>
+      <c r="AD2" s="321"/>
+      <c r="AE2" s="321"/>
+      <c r="AF2" s="321"/>
+      <c r="AG2" s="321"/>
+      <c r="AH2" s="321"/>
+      <c r="AI2" s="321"/>
+      <c r="AJ2" s="321"/>
+      <c r="AK2" s="321"/>
+      <c r="AL2" s="321"/>
+      <c r="AM2" s="321"/>
+      <c r="AN2" s="321"/>
+      <c r="AO2" s="333"/>
+      <c r="AP2" s="333"/>
+      <c r="AQ2" s="333"/>
+      <c r="AR2" s="333"/>
+      <c r="AS2" s="333"/>
+      <c r="AT2" s="333"/>
+      <c r="AU2" s="333"/>
+      <c r="AV2" s="333"/>
+      <c r="AW2" s="333"/>
+      <c r="AX2" s="333"/>
+      <c r="AY2" s="333"/>
+      <c r="AZ2" s="333"/>
+      <c r="BA2" s="333"/>
+      <c r="BB2" s="333"/>
+      <c r="BC2" s="333"/>
+      <c r="BD2" s="333"/>
+      <c r="BE2" s="333"/>
+      <c r="BF2" s="333"/>
+      <c r="BG2" s="315" t="s">
+        <v>1</v>
+      </c>
+      <c r="BH2" s="315"/>
+      <c r="BI2" s="321" t="s">
         <v>2</v>
       </c>
-      <c r="BJ2" s="324"/>
-      <c r="BK2" s="329" t="s">
+      <c r="BJ2" s="321"/>
+      <c r="BK2" s="322" t="s">
         <v>7</v>
       </c>
-      <c r="BL2" s="329" t="s">
+      <c r="BL2" s="322" t="s">
         <v>97</v>
       </c>
       <c r="BM2" s="27" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:68" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="3" spans="1:68" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A3" s="189" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="316"/>
-      <c r="C3" s="319"/>
-      <c r="D3" s="322"/>
-      <c r="E3" s="326">
-        <v>1</v>
-      </c>
-      <c r="F3" s="326"/>
-      <c r="G3" s="326">
+      <c r="B3" s="325"/>
+      <c r="C3" s="328"/>
+      <c r="D3" s="331"/>
+      <c r="E3" s="315">
+        <v>1</v>
+      </c>
+      <c r="F3" s="315"/>
+      <c r="G3" s="315">
         <v>2</v>
       </c>
-      <c r="H3" s="326"/>
-      <c r="I3" s="326">
+      <c r="H3" s="315"/>
+      <c r="I3" s="315">
         <v>3</v>
       </c>
-      <c r="J3" s="326"/>
-      <c r="K3" s="326">
+      <c r="J3" s="315"/>
+      <c r="K3" s="315">
         <v>7</v>
       </c>
-      <c r="L3" s="326"/>
-      <c r="M3" s="326">
+      <c r="L3" s="315"/>
+      <c r="M3" s="315">
         <v>8</v>
       </c>
-      <c r="N3" s="326"/>
-      <c r="O3" s="326">
+      <c r="N3" s="315"/>
+      <c r="O3" s="315">
         <v>9</v>
       </c>
-      <c r="P3" s="326"/>
-      <c r="Q3" s="326">
+      <c r="P3" s="315"/>
+      <c r="Q3" s="315">
         <v>10</v>
       </c>
-      <c r="R3" s="326"/>
-      <c r="S3" s="326">
+      <c r="R3" s="315"/>
+      <c r="S3" s="315">
         <v>13</v>
       </c>
-      <c r="T3" s="326"/>
-      <c r="U3" s="326">
+      <c r="T3" s="315"/>
+      <c r="U3" s="315">
         <v>14</v>
       </c>
-      <c r="V3" s="326"/>
-      <c r="W3" s="326">
+      <c r="V3" s="315"/>
+      <c r="W3" s="315">
         <v>15</v>
       </c>
-      <c r="X3" s="326"/>
-      <c r="Y3" s="326">
+      <c r="X3" s="315"/>
+      <c r="Y3" s="315">
         <v>16</v>
       </c>
-      <c r="Z3" s="326"/>
-      <c r="AA3" s="326">
+      <c r="Z3" s="315"/>
+      <c r="AA3" s="315">
         <v>17</v>
       </c>
-      <c r="AB3" s="326"/>
-      <c r="AC3" s="326">
+      <c r="AB3" s="315"/>
+      <c r="AC3" s="315">
         <v>20</v>
       </c>
-      <c r="AD3" s="326"/>
-      <c r="AE3" s="326">
+      <c r="AD3" s="315"/>
+      <c r="AE3" s="315">
         <v>21</v>
       </c>
-      <c r="AF3" s="326"/>
-      <c r="AG3" s="326">
+      <c r="AF3" s="315"/>
+      <c r="AG3" s="315">
         <v>22</v>
       </c>
-      <c r="AH3" s="326"/>
-      <c r="AI3" s="326">
+      <c r="AH3" s="315"/>
+      <c r="AI3" s="315">
         <v>23</v>
       </c>
-      <c r="AJ3" s="326"/>
-      <c r="AK3" s="326">
+      <c r="AJ3" s="315"/>
+      <c r="AK3" s="315">
         <v>24</v>
       </c>
-      <c r="AL3" s="326"/>
-      <c r="AM3" s="326">
+      <c r="AL3" s="315"/>
+      <c r="AM3" s="315">
         <v>27</v>
       </c>
-      <c r="AN3" s="326"/>
-      <c r="AO3" s="327">
+      <c r="AN3" s="315"/>
+      <c r="AO3" s="318">
         <v>28</v>
       </c>
-      <c r="AP3" s="326"/>
-      <c r="AQ3" s="328">
+      <c r="AP3" s="315"/>
+      <c r="AQ3" s="317">
         <v>29</v>
       </c>
-      <c r="AR3" s="327"/>
-      <c r="AS3" s="328">
+      <c r="AR3" s="318"/>
+      <c r="AS3" s="317">
         <v>30</v>
       </c>
-      <c r="AT3" s="327"/>
-      <c r="AU3" s="328">
+      <c r="AT3" s="318"/>
+      <c r="AU3" s="317">
         <v>31</v>
       </c>
-      <c r="AV3" s="327"/>
-      <c r="AW3" s="326"/>
-      <c r="AX3" s="326"/>
-      <c r="AY3" s="326"/>
-      <c r="AZ3" s="326"/>
-      <c r="BA3" s="328"/>
-      <c r="BB3" s="327"/>
-      <c r="BC3" s="328"/>
-      <c r="BD3" s="327"/>
-      <c r="BE3" s="328"/>
-      <c r="BF3" s="331"/>
-      <c r="BG3" s="332" t="s">
+      <c r="AV3" s="318"/>
+      <c r="AW3" s="315"/>
+      <c r="AX3" s="315"/>
+      <c r="AY3" s="315"/>
+      <c r="AZ3" s="315"/>
+      <c r="BA3" s="317"/>
+      <c r="BB3" s="318"/>
+      <c r="BC3" s="317"/>
+      <c r="BD3" s="318"/>
+      <c r="BE3" s="317"/>
+      <c r="BF3" s="319"/>
+      <c r="BG3" s="320" t="s">
         <v>23</v>
       </c>
-      <c r="BH3" s="326" t="s">
+      <c r="BH3" s="315" t="s">
         <v>19</v>
       </c>
-      <c r="BI3" s="332" t="s">
+      <c r="BI3" s="320" t="s">
         <v>24</v>
       </c>
-      <c r="BJ3" s="326" t="s">
+      <c r="BJ3" s="315" t="s">
         <v>19</v>
       </c>
-      <c r="BK3" s="333"/>
-      <c r="BL3" s="329"/>
+      <c r="BK3" s="323"/>
+      <c r="BL3" s="322"/>
       <c r="BM3" s="27" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:68" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="4" spans="1:68" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A4" s="189" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="317"/>
-      <c r="C4" s="320"/>
-      <c r="D4" s="323"/>
+      <c r="B4" s="326"/>
+      <c r="C4" s="329"/>
+      <c r="D4" s="332"/>
       <c r="E4" s="218" t="s">
         <v>25</v>
       </c>
@@ -13855,23 +13855,23 @@
       <c r="BF4" s="142" t="s">
         <v>26</v>
       </c>
-      <c r="BG4" s="326"/>
-      <c r="BH4" s="326"/>
-      <c r="BI4" s="326"/>
-      <c r="BJ4" s="326"/>
-      <c r="BK4" s="333"/>
-      <c r="BL4" s="329"/>
+      <c r="BG4" s="315"/>
+      <c r="BH4" s="315"/>
+      <c r="BI4" s="315"/>
+      <c r="BJ4" s="315"/>
+      <c r="BK4" s="323"/>
+      <c r="BL4" s="322"/>
       <c r="BM4" s="27" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:68" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="5" spans="1:68" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A5" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="145">
         <f>SUBTOTAL(103,C$5:C5)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="192" t="s">
         <v>167</v>
@@ -13963,7 +13963,7 @@
       </c>
       <c r="B6" s="145">
         <f>SUBTOTAL(103,C$5:C6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="150" t="s">
         <v>29</v>
@@ -14087,13 +14087,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="7" spans="1:68" s="27" customFormat="1" ht="27" hidden="1">
+    <row r="7" spans="1:68" s="27" customFormat="1" ht="28.8">
       <c r="A7" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="145">
         <f>SUBTOTAL(103,C$5:C7)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" s="192" t="s">
         <v>224</v>
@@ -14179,11 +14179,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="8" spans="1:68" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="8" spans="1:68" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A8" s="189"/>
       <c r="B8" s="145">
         <f>SUBTOTAL(103,C$5:C8)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" s="151" t="s">
         <v>175</v>
@@ -14269,13 +14269,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="9" spans="1:68" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="9" spans="1:68" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A9" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="145">
         <f>SUBTOTAL(103,C$5:C9)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C9" s="151" t="s">
         <v>31</v>
@@ -14361,11 +14361,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="10" spans="1:68" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="10" spans="1:68" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A10" s="189"/>
       <c r="B10" s="145">
         <f>SUBTOTAL(103,C$5:C10)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C10" s="192" t="s">
         <v>193</v>
@@ -14451,13 +14451,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="11" spans="1:68" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="11" spans="1:68" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A11" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="145">
         <f>SUBTOTAL(103,C$5:C11)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C11" s="199" t="s">
         <v>173</v>
@@ -14543,11 +14543,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="12" spans="1:68" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="12" spans="1:68" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A12" s="189"/>
       <c r="B12" s="145">
         <f>SUBTOTAL(103,C$5:C12)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C12" s="27" t="s">
         <v>185</v>
@@ -14633,11 +14633,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="13" spans="1:68" s="27" customFormat="1" ht="18.75" hidden="1" customHeight="1">
+    <row r="13" spans="1:68" s="27" customFormat="1" ht="18.75" customHeight="1">
       <c r="A13" s="189"/>
       <c r="B13" s="145">
         <f>SUBTOTAL(103,C$5:C13)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C13" s="154" t="s">
         <v>181</v>
@@ -14723,13 +14723,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="14" spans="1:68" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="14" spans="1:68" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A14" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="145">
         <f>SUBTOTAL(103,C$5:C14)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C14" s="192" t="s">
         <v>34</v>
@@ -14853,11 +14853,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="15" spans="1:68" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="15" spans="1:68" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A15" s="189"/>
       <c r="B15" s="145">
         <f>SUBTOTAL(103,C$5:C15)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C15" s="192" t="s">
         <v>177</v>
@@ -14981,11 +14981,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="16" spans="1:68" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="16" spans="1:68" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A16" s="189"/>
       <c r="B16" s="145">
         <f>SUBTOTAL(103,C$5:C16)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C16" s="214" t="s">
         <v>217</v>
@@ -15073,13 +15073,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="17" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="17" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A17" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B17" s="145">
         <f>SUBTOTAL(103,C$5:C17)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C17" s="27" t="s">
         <v>174</v>
@@ -15199,13 +15199,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="18" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="18" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A18" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="145">
         <f>SUBTOTAL(103,C$5:C18)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C18" s="192" t="s">
         <v>195</v>
@@ -15293,11 +15293,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="19" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="19" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A19" s="189"/>
       <c r="B19" s="145">
         <f>SUBTOTAL(103,C$5:C19)</f>
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C19" s="154" t="s">
         <v>152</v>
@@ -15383,11 +15383,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="20" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="20" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A20" s="189"/>
       <c r="B20" s="145">
         <f>SUBTOTAL(103,C$5:C20)</f>
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C20" s="265" t="s">
         <v>339</v>
@@ -15493,13 +15493,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="21" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="21" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A21" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="145">
         <f>SUBTOTAL(103,C$5:C21)</f>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C21" s="267" t="s">
         <v>198</v>
@@ -15593,13 +15593,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="22" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="22" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A22" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B22" s="145">
         <f>SUBTOTAL(103,C$5:C22)</f>
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C22" s="192" t="s">
         <v>164</v>
@@ -15685,13 +15685,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="23" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="23" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A23" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B23" s="145">
         <f>SUBTOTAL(103,C$5:C23)</f>
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C23" s="192" t="s">
         <v>165</v>
@@ -15777,13 +15777,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="24" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="24" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A24" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B24" s="145">
         <f>SUBTOTAL(103,C$5:C24)</f>
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C24" s="192" t="s">
         <v>316</v>
@@ -15873,13 +15873,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="25" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="25" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A25" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="145">
         <f>SUBTOTAL(103,C$5:C25)</f>
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C25" s="192" t="s">
         <v>42</v>
@@ -15969,11 +15969,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="26" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="26" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A26" s="189"/>
       <c r="B26" s="145">
         <f>SUBTOTAL(103,C$5:C26)</f>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C26" s="151" t="s">
         <v>343</v>
@@ -16063,13 +16063,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="27" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="27" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A27" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="145">
         <f>SUBTOTAL(103,C$5:C27)</f>
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C27" s="192" t="s">
         <v>45</v>
@@ -16165,7 +16165,7 @@
       </c>
       <c r="B28" s="145">
         <f>SUBTOTAL(103,C$5:C28)</f>
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C28" s="192" t="s">
         <v>39</v>
@@ -16293,13 +16293,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="29" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="29" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A29" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B29" s="145">
         <f>SUBTOTAL(103,C$5:C29)</f>
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C29" s="150" t="s">
         <v>37</v>
@@ -16397,13 +16397,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="30" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="30" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A30" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B30" s="145">
         <f>SUBTOTAL(103,C$5:C30)</f>
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C30" s="192" t="s">
         <v>44</v>
@@ -16491,11 +16491,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="31" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="31" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A31" s="189"/>
       <c r="B31" s="145">
         <f>SUBTOTAL(103,C$5:C31)</f>
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C31" s="192" t="s">
         <v>232</v>
@@ -16585,7 +16585,7 @@
       <c r="A32" s="189"/>
       <c r="B32" s="145">
         <f>SUBTOTAL(103,C$5:C32)</f>
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C32" s="192" t="s">
         <v>46</v>
@@ -16675,13 +16675,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="33" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="33" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A33" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B33" s="145">
         <f>SUBTOTAL(103,C$5:C33)</f>
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C33" s="154" t="s">
         <v>48</v>
@@ -16781,13 +16781,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="34" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="34" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A34" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B34" s="145">
         <f>SUBTOTAL(103,C$5:C34)</f>
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C34" s="154" t="s">
         <v>50</v>
@@ -16899,13 +16899,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="35" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="35" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A35" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B35" s="145">
         <f>SUBTOTAL(103,C$5:C35)</f>
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C35" s="154" t="s">
         <v>52</v>
@@ -17005,11 +17005,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="36" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="36" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A36" s="189"/>
       <c r="B36" s="145">
         <f>SUBTOTAL(103,C$5:C36)</f>
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C36" s="154" t="s">
         <v>196</v>
@@ -17095,11 +17095,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="37" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="37" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A37" s="189"/>
       <c r="B37" s="145">
         <f>SUBTOTAL(103,C$5:C37)</f>
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C37" s="154" t="s">
         <v>233</v>
@@ -17185,13 +17185,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="38" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="38" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A38" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B38" s="145">
         <f>SUBTOTAL(103,C$5:C38)</f>
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C38" s="154" t="s">
         <v>234</v>
@@ -17309,11 +17309,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="39" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="39" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A39" s="189"/>
       <c r="B39" s="145">
         <f>SUBTOTAL(103,C$5:C39)</f>
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C39" s="154" t="s">
         <v>151</v>
@@ -17399,13 +17399,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="40" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="40" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A40" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B40" s="145">
         <f>SUBTOTAL(103,C$5:C40)</f>
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C40" s="154" t="s">
         <v>235</v>
@@ -17507,13 +17507,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="41" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="41" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A41" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B41" s="145">
         <f>SUBTOTAL(103,C$5:C41)</f>
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C41" s="154" t="s">
         <v>236</v>
@@ -17639,13 +17639,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="42" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="42" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A42" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B42" s="145">
         <f>SUBTOTAL(103,C$5:C42)</f>
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C42" s="154" t="s">
         <v>237</v>
@@ -17731,11 +17731,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="43" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="43" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A43" s="189"/>
       <c r="B43" s="145">
         <f>SUBTOTAL(103,C$5:C43)</f>
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C43" s="154" t="s">
         <v>55</v>
@@ -17829,13 +17829,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="44" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="44" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A44" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B44" s="145">
         <f>SUBTOTAL(103,C$5:C44)</f>
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C44" s="154" t="s">
         <v>238</v>
@@ -17959,11 +17959,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="45" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="45" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A45" s="189"/>
       <c r="B45" s="145">
         <f>SUBTOTAL(103,C$5:C45)</f>
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C45" s="154" t="s">
         <v>59</v>
@@ -18049,13 +18049,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="46" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="46" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A46" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B46" s="145">
         <f>SUBTOTAL(103,C$5:C46)</f>
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C46" s="154" t="s">
         <v>239</v>
@@ -18151,11 +18151,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="47" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="47" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A47" s="189"/>
       <c r="B47" s="145">
         <f>SUBTOTAL(103,C$5:C47)</f>
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C47" s="154" t="s">
         <v>62</v>
@@ -18241,13 +18241,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="48" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="48" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A48" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B48" s="145">
         <f>SUBTOTAL(103,C$5:C48)</f>
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C48" s="154" t="s">
         <v>63</v>
@@ -18335,11 +18335,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="49" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="49" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A49" s="189"/>
       <c r="B49" s="145">
         <f>SUBTOTAL(103,C$5:C49)</f>
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="C49" s="154" t="s">
         <v>240</v>
@@ -18435,13 +18435,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="50" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="50" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A50" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B50" s="145">
         <f>SUBTOTAL(103,C$5:C50)</f>
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C50" s="150" t="s">
         <v>241</v>
@@ -18527,13 +18527,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="51" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="51" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A51" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B51" s="145">
         <f>SUBTOTAL(103,C$5:C51)</f>
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C51" s="154" t="s">
         <v>204</v>
@@ -18621,11 +18621,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="52" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="52" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A52" s="189"/>
       <c r="B52" s="145">
         <f>SUBTOTAL(103,C$5:C52)</f>
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C52" s="154" t="s">
         <v>242</v>
@@ -18719,11 +18719,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="53" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="53" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A53" s="189"/>
       <c r="B53" s="145">
         <f>SUBTOTAL(103,C$5:C53)</f>
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="C53" s="154" t="s">
         <v>243</v>
@@ -18809,13 +18809,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="54" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="54" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A54" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B54" s="145">
         <f>SUBTOTAL(103,C$5:C54)</f>
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C54" s="154" t="s">
         <v>65</v>
@@ -18927,13 +18927,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="55" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="55" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A55" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B55" s="145">
         <f>SUBTOTAL(103,C$5:C55)</f>
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="C55" s="154" t="s">
         <v>244</v>
@@ -19019,11 +19019,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="56" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="56" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A56" s="189"/>
       <c r="B56" s="145">
         <f>SUBTOTAL(103,C$5:C56)</f>
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C56" s="154" t="s">
         <v>245</v>
@@ -19113,13 +19113,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="57" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="57" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A57" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B57" s="145">
         <f>SUBTOTAL(103,C$5:C57)</f>
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C57" s="154" t="s">
         <v>246</v>
@@ -19205,11 +19205,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="58" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="58" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A58" s="189"/>
       <c r="B58" s="145">
         <f>SUBTOTAL(103,C$5:C58)</f>
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C58" s="154" t="s">
         <v>247</v>
@@ -19295,11 +19295,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="59" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="59" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A59" s="189"/>
       <c r="B59" s="145">
         <f>SUBTOTAL(103,C$5:C59)</f>
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C59" s="154" t="s">
         <v>248</v>
@@ -19385,11 +19385,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="60" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="60" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A60" s="189"/>
       <c r="B60" s="145">
         <f>SUBTOTAL(103,C$5:C60)</f>
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C60" s="154" t="s">
         <v>249</v>
@@ -19495,11 +19495,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="61" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="61" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A61" s="189"/>
       <c r="B61" s="145">
         <f>SUBTOTAL(103,C$5:C61)</f>
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C61" s="154" t="s">
         <v>250</v>
@@ -19587,11 +19587,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="62" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="62" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A62" s="189"/>
       <c r="B62" s="145">
         <f>SUBTOTAL(103,C$5:C62)</f>
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C62" s="154" t="s">
         <v>251</v>
@@ -19677,11 +19677,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="63" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="63" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A63" s="189"/>
       <c r="B63" s="145">
         <f>SUBTOTAL(103,C$5:C63)</f>
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C63" s="154" t="s">
         <v>252</v>
@@ -19767,13 +19767,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="64" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="64" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A64" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B64" s="145">
         <f>SUBTOTAL(103,C$5:C64)</f>
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C64" s="154" t="s">
         <v>66</v>
@@ -19901,11 +19901,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="65" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="65" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A65" s="189"/>
       <c r="B65" s="145">
         <f>SUBTOTAL(103,C$5:C65)</f>
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C65" s="154" t="s">
         <v>222</v>
@@ -20029,7 +20029,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="66" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="66" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A66" s="189"/>
       <c r="B66" s="145"/>
       <c r="C66" s="270" t="s">
@@ -20120,13 +20120,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="67" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="67" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A67" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B67" s="145">
         <f>SUBTOTAL(103,C$5:C67)</f>
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C67" s="154" t="s">
         <v>253</v>
@@ -20256,11 +20256,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="68" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="68" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A68" s="189"/>
       <c r="B68" s="145">
         <f>SUBTOTAL(103,C$5:C68)</f>
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C68" s="154" t="s">
         <v>238</v>
@@ -20348,11 +20348,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="69" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="69" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A69" s="189"/>
       <c r="B69" s="145">
         <f>SUBTOTAL(103,C$5:C69)</f>
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C69" s="154" t="s">
         <v>254</v>
@@ -20438,13 +20438,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="70" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="70" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A70" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B70" s="145">
         <f>SUBTOTAL(103,C$5:C70)</f>
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="C70" s="154" t="s">
         <v>255</v>
@@ -20530,11 +20530,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="71" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="71" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A71" s="189"/>
       <c r="B71" s="145">
         <f>SUBTOTAL(103,C$5:C71)</f>
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C71" s="154" t="s">
         <v>256</v>
@@ -20620,13 +20620,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="72" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="72" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A72" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B72" s="145">
         <f>SUBTOTAL(103,C$5:C72)</f>
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C72" s="154" t="s">
         <v>69</v>
@@ -20732,11 +20732,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="73" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="73" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A73" s="189"/>
       <c r="B73" s="145">
         <f>SUBTOTAL(103,C$5:C73)</f>
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="C73" s="154" t="s">
         <v>257</v>
@@ -20824,13 +20824,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="74" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="74" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A74" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B74" s="145">
         <f>SUBTOTAL(103,C$5:C74)</f>
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C74" s="154" t="s">
         <v>258</v>
@@ -20916,11 +20916,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="75" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="75" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A75" s="189"/>
       <c r="B75" s="145">
         <f>SUBTOTAL(103,C$5:C75)</f>
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="C75" s="154" t="s">
         <v>214</v>
@@ -21020,11 +21020,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="76" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="76" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A76" s="189"/>
       <c r="B76" s="145">
         <f>SUBTOTAL(103,C$5:C76)</f>
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="C76" s="154" t="s">
         <v>259</v>
@@ -21118,11 +21118,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="77" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="77" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A77" s="189"/>
       <c r="B77" s="145">
         <f>SUBTOTAL(103,C$5:C77)</f>
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="C77" s="154" t="s">
         <v>220</v>
@@ -21210,11 +21210,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="78" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="78" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A78" s="189"/>
       <c r="B78" s="145">
         <f>SUBTOTAL(103,C$5:C78)</f>
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C78" s="254" t="s">
         <v>312</v>
@@ -21303,11 +21303,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="79" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="79" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A79" s="189"/>
       <c r="B79" s="145">
         <f>SUBTOTAL(103,C$5:C79)</f>
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C79" s="154" t="s">
         <v>221</v>
@@ -21395,11 +21395,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="80" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="80" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A80" s="189"/>
       <c r="B80" s="145">
         <f>SUBTOTAL(103,C$5:C80)</f>
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="C80" s="154" t="s">
         <v>228</v>
@@ -21485,11 +21485,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="81" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="81" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A81" s="189"/>
       <c r="B81" s="145">
         <f>SUBTOTAL(103,C$5:C81)</f>
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="C81" s="154" t="s">
         <v>229</v>
@@ -21575,11 +21575,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="82" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="82" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A82" s="189"/>
       <c r="B82" s="145">
         <f>SUBTOTAL(103,C$5:C82)</f>
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="C82" s="265" t="s">
         <v>340</v>
@@ -21667,13 +21667,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="83" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="83" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A83" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B83" s="145">
         <f>SUBTOTAL(103,C$5:C83)</f>
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="C83" s="150" t="s">
         <v>74</v>
@@ -21759,11 +21759,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="84" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="84" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A84" s="189"/>
       <c r="B84" s="145">
         <f>SUBTOTAL(103,C$5:C84)</f>
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="C84" s="154" t="s">
         <v>260</v>
@@ -21849,11 +21849,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="85" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="85" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A85" s="189"/>
       <c r="B85" s="145">
         <f>SUBTOTAL(103,C$5:C85)</f>
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="C85" s="154" t="s">
         <v>261</v>
@@ -21949,13 +21949,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="86" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="86" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A86" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B86" s="145">
         <f>SUBTOTAL(103,C$5:C86)</f>
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="C86" s="154" t="s">
         <v>71</v>
@@ -22045,11 +22045,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="87" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="87" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A87" s="189"/>
       <c r="B87" s="145">
         <f>SUBTOTAL(103,C$5:C87)</f>
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="C87" s="154" t="s">
         <v>205</v>
@@ -22135,11 +22135,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="88" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="88" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A88" s="189"/>
       <c r="B88" s="145">
         <f>SUBTOTAL(103,C$5:C88)</f>
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="C88" s="154" t="s">
         <v>73</v>
@@ -22225,13 +22225,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="89" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="89" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A89" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B89" s="145">
         <f>SUBTOTAL(103,C$5:C89)</f>
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="C89" s="154" t="s">
         <v>262</v>
@@ -22317,11 +22317,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="90" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="90" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A90" s="189"/>
       <c r="B90" s="145">
         <f>SUBTOTAL(103,C$5:C90)</f>
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C90" s="154" t="s">
         <v>210</v>
@@ -22407,13 +22407,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="91" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="91" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A91" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B91" s="145">
         <f>SUBTOTAL(103,C$5:C91)</f>
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="C91" s="150" t="s">
         <v>263</v>
@@ -22527,13 +22527,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="92" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="92" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A92" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B92" s="145">
         <f>SUBTOTAL(103,C$5:C92)</f>
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="C92" s="154" t="s">
         <v>78</v>
@@ -22627,13 +22627,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="93" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="93" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A93" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B93" s="145">
         <f>SUBTOTAL(103,C$5:C93)</f>
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="C93" s="150" t="s">
         <v>264</v>
@@ -22749,11 +22749,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="94" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="94" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A94" s="189"/>
       <c r="B94" s="145">
         <f>SUBTOTAL(103,C$5:C94)</f>
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="C94" s="150" t="s">
         <v>265</v>
@@ -22839,13 +22839,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="95" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="95" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A95" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B95" s="145">
         <f>SUBTOTAL(103,C$5:C95)</f>
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="C95" s="154" t="s">
         <v>266</v>
@@ -22949,11 +22949,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="96" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="96" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A96" s="189"/>
       <c r="B96" s="145">
         <f>SUBTOTAL(103,C$5:C96)</f>
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="C96" s="154" t="s">
         <v>267</v>
@@ -23039,11 +23039,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="97" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="97" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A97" s="189"/>
       <c r="B97" s="145">
         <f>SUBTOTAL(103,C$5:C97)</f>
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C97" s="150" t="s">
         <v>268</v>
@@ -23163,11 +23163,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="98" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="98" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A98" s="189"/>
       <c r="B98" s="145">
         <f>SUBTOTAL(103,C$5:C98)</f>
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="C98" s="154" t="s">
         <v>77</v>
@@ -23287,13 +23287,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="99" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="99" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A99" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B99" s="145">
         <f>SUBTOTAL(103,C$5:C99)</f>
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="C99" s="150" t="s">
         <v>80</v>
@@ -23381,11 +23381,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="100" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="100" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A100" s="189"/>
       <c r="B100" s="145">
         <f>SUBTOTAL(103,C$5:C100)</f>
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="C100" s="150" t="s">
         <v>295</v>
@@ -23471,11 +23471,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="101" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="101" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A101" s="189"/>
       <c r="B101" s="145">
         <f>SUBTOTAL(103,C$5:C101)</f>
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="C101" s="154" t="s">
         <v>269</v>
@@ -23571,13 +23571,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="102" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="102" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A102" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B102" s="145">
         <f>SUBTOTAL(103,C$5:C102)</f>
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="C102" s="154" t="s">
         <v>270</v>
@@ -23663,11 +23663,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="103" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="103" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A103" s="189"/>
       <c r="B103" s="145">
         <f>SUBTOTAL(103,C$5:C103)</f>
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="C103" s="154" t="s">
         <v>271</v>
@@ -23753,11 +23753,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="104" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="104" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A104" s="189"/>
       <c r="B104" s="145">
         <f>SUBTOTAL(103,C$5:C104)</f>
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="C104" s="154" t="s">
         <v>272</v>
@@ -23843,13 +23843,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="105" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="105" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A105" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B105" s="145">
         <f>SUBTOTAL(103,C$5:C105)</f>
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="C105" s="154" t="s">
         <v>273</v>
@@ -23937,11 +23937,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="106" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="106" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A106" s="189"/>
       <c r="B106" s="145">
         <f>SUBTOTAL(103,C$5:C106)</f>
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="C106" s="154" t="s">
         <v>274</v>
@@ -24027,11 +24027,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="107" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="107" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A107" s="189"/>
       <c r="B107" s="145">
         <f>SUBTOTAL(103,C$5:C107)</f>
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="C107" s="154" t="s">
         <v>275</v>
@@ -24119,13 +24119,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="108" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="108" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A108" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B108" s="145">
         <f>SUBTOTAL(103,C$5:C108)</f>
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="C108" s="150" t="s">
         <v>276</v>
@@ -24213,11 +24213,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="109" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="109" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A109" s="189"/>
       <c r="B109" s="145">
         <f>SUBTOTAL(103,C$5:C109)</f>
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="C109" s="145" t="s">
         <v>277</v>
@@ -24303,11 +24303,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="110" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="110" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A110" s="189"/>
       <c r="B110" s="145">
         <f>SUBTOTAL(103,C$5:C110)</f>
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="C110" s="145" t="s">
         <v>278</v>
@@ -24393,11 +24393,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="111" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="111" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A111" s="189"/>
       <c r="B111" s="145">
         <f>SUBTOTAL(103,C$5:C111)</f>
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="C111" s="154" t="s">
         <v>84</v>
@@ -24483,11 +24483,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="112" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="112" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A112" s="189"/>
       <c r="B112" s="145">
         <f>SUBTOTAL(103,C$5:C112)</f>
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="C112" s="154" t="s">
         <v>85</v>
@@ -24577,11 +24577,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="113" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="113" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A113" s="189"/>
       <c r="B113" s="145">
         <f>SUBTOTAL(103,C$5:C113)</f>
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="C113" s="254" t="s">
         <v>313</v>
@@ -24681,11 +24681,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="114" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="114" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A114" s="189"/>
       <c r="B114" s="145">
         <f>SUBTOTAL(103,C$5:C114)</f>
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="C114" s="154" t="s">
         <v>279</v>
@@ -24803,11 +24803,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="115" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="115" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A115" s="189"/>
       <c r="B115" s="145">
         <f>SUBTOTAL(103,C$5:C115)</f>
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="C115" s="154" t="s">
         <v>83</v>
@@ -24899,11 +24899,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="116" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="116" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A116" s="189"/>
       <c r="B116" s="145">
         <f>SUBTOTAL(103,C$5:C116)</f>
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="C116" s="154" t="s">
         <v>280</v>
@@ -25001,11 +25001,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="117" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="117" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A117" s="189"/>
       <c r="B117" s="145">
         <f>SUBTOTAL(103,C$5:C117)</f>
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="C117" s="154" t="s">
         <v>281</v>
@@ -25091,11 +25091,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="118" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="118" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A118" s="189"/>
       <c r="B118" s="145">
         <f>SUBTOTAL(103,C$5:C118)</f>
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="C118" s="154" t="s">
         <v>282</v>
@@ -25199,13 +25199,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="119" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="119" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A119" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B119" s="145">
         <f>SUBTOTAL(103,C$5:C119)</f>
-        <v>65</v>
+        <v>115</v>
       </c>
       <c r="C119" s="154" t="s">
         <v>283</v>
@@ -25291,13 +25291,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="120" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="120" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A120" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B120" s="145">
         <f>SUBTOTAL(103,C$5:C120)</f>
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="C120" s="154" t="s">
         <v>87</v>
@@ -25383,13 +25383,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="121" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="121" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A121" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B121" s="145">
         <f>SUBTOTAL(103,C$5:C121)</f>
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="C121" s="154" t="s">
         <v>284</v>
@@ -25475,13 +25475,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="122" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="122" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A122" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B122" s="145">
         <f>SUBTOTAL(103,C$5:C122)</f>
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="C122" s="154" t="s">
         <v>86</v>
@@ -25611,13 +25611,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="123" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="123" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A123" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B123" s="145">
         <f>SUBTOTAL(103,C$5:C123)</f>
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="C123" s="154" t="s">
         <v>75</v>
@@ -25717,11 +25717,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="124" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="124" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A124" s="189"/>
       <c r="B124" s="145">
         <f>SUBTOTAL(103,C$5:C124)</f>
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="C124" s="154" t="s">
         <v>285</v>
@@ -25807,13 +25807,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="125" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="125" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A125" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B125" s="145">
         <f>SUBTOTAL(103,C$5:C125)</f>
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="C125" s="154" t="s">
         <v>66</v>
@@ -25899,11 +25899,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="126" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="126" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A126" s="189"/>
       <c r="B126" s="145">
         <f>SUBTOTAL(103,C$5:C126)</f>
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="C126" s="154" t="s">
         <v>286</v>
@@ -26029,11 +26029,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="127" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="127" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A127" s="189"/>
       <c r="B127" s="145">
         <f>SUBTOTAL(103,C$5:C127)</f>
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="C127" s="154" t="s">
         <v>287</v>
@@ -26119,11 +26119,11 @@
         <v>×</v>
       </c>
     </row>
-    <row r="128" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="128" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A128" s="189"/>
       <c r="B128" s="145">
         <f>SUBTOTAL(103,C$5:C128)</f>
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="C128" s="154" t="s">
         <v>288</v>
@@ -26243,11 +26243,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="129" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="129" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A129" s="189"/>
       <c r="B129" s="145">
         <f>SUBTOTAL(103,C$5:C129)</f>
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C129" s="154" t="s">
         <v>289</v>
@@ -26333,13 +26333,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="130" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="130" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A130" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B130" s="145">
         <f>SUBTOTAL(103,C$5:C130)</f>
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="C130" s="154" t="s">
         <v>290</v>
@@ -26425,13 +26425,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="131" spans="1:65" s="27" customFormat="1" ht="24.95" hidden="1" customHeight="1">
+    <row r="131" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A131" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B131" s="145">
         <f>SUBTOTAL(103,C$5:C131)</f>
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="C131" s="154" t="s">
         <v>291</v>
@@ -26517,13 +26517,13 @@
         <v>×</v>
       </c>
     </row>
-    <row r="132" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="132" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A132" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B132" s="145">
         <f>SUBTOTAL(103,C$5:C132)</f>
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="C132" s="154" t="s">
         <v>292</v>
@@ -26635,11 +26635,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="133" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="133" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A133" s="189"/>
       <c r="B133" s="145">
         <f>SUBTOTAL(103,C$5:C133)</f>
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="C133" s="268" t="s">
         <v>344</v>
@@ -26733,11 +26733,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="134" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="134" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A134" s="189"/>
       <c r="B134" s="145">
         <f>SUBTOTAL(103,C$5:C134)</f>
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="C134" s="154" t="s">
         <v>231</v>
@@ -26827,11 +26827,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="135" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="135" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A135" s="189"/>
       <c r="B135" s="145">
         <f>SUBTOTAL(103,C$5:C135)</f>
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="C135" s="265" t="s">
         <v>341</v>
@@ -26923,11 +26923,11 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="136" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="136" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A136" s="189"/>
       <c r="B136" s="145">
         <f>SUBTOTAL(103,C$5:C136)</f>
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="C136" s="154" t="s">
         <v>293</v>
@@ -27047,13 +27047,13 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="137" spans="1:65" s="27" customFormat="1" ht="24.95" customHeight="1">
+    <row r="137" spans="1:65" s="27" customFormat="1" ht="24.9" customHeight="1">
       <c r="A137" s="189" t="s">
         <v>27</v>
       </c>
       <c r="B137" s="145">
         <f>SUBTOTAL(103,C$5:C137)</f>
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="C137" s="154" t="s">
         <v>294</v>
@@ -27415,38 +27415,32 @@
         <f t="shared" si="16"/>
         <v>616</v>
       </c>
-      <c r="BJ138" s="330">
+      <c r="BJ138" s="316">
         <f>SUM(BK5:BK137)</f>
         <v>51200</v>
       </c>
-      <c r="BK138" s="330"/>
+      <c r="BK138" s="316"/>
       <c r="BL138" s="229"/>
       <c r="BM138" s="223" t="s">
         <v>92</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="BM1:BM138" xr:uid="{055714F9-7884-4ECE-AC8C-26C53B164898}">
-    <filterColumn colId="0">
-      <filters blank="1">
-        <filter val="."/>
-        <filter val="OK"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="BM1:BM138" xr:uid="{055714F9-7884-4ECE-AC8C-26C53B164898}"/>
   <mergeCells count="41">
-    <mergeCell ref="E1:BJ1"/>
-    <mergeCell ref="AW3:AX3"/>
-    <mergeCell ref="BJ3:BJ4"/>
-    <mergeCell ref="BJ138:BK138"/>
-    <mergeCell ref="BA3:BB3"/>
-    <mergeCell ref="BC3:BD3"/>
-    <mergeCell ref="BE3:BF3"/>
-    <mergeCell ref="BG3:BG4"/>
-    <mergeCell ref="BH3:BH4"/>
-    <mergeCell ref="BI3:BI4"/>
-    <mergeCell ref="BI2:BJ2"/>
-    <mergeCell ref="BK2:BK4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:BF2"/>
+    <mergeCell ref="BG2:BH2"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AM3:AN3"/>
+    <mergeCell ref="AO3:AP3"/>
+    <mergeCell ref="AQ3:AR3"/>
+    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="AU3:AV3"/>
     <mergeCell ref="BL2:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
@@ -27463,19 +27457,18 @@
     <mergeCell ref="AG3:AH3"/>
     <mergeCell ref="AI3:AJ3"/>
     <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:BF2"/>
-    <mergeCell ref="BG2:BH2"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AM3:AN3"/>
-    <mergeCell ref="AO3:AP3"/>
-    <mergeCell ref="AQ3:AR3"/>
-    <mergeCell ref="AS3:AT3"/>
-    <mergeCell ref="AU3:AV3"/>
+    <mergeCell ref="E1:BJ1"/>
+    <mergeCell ref="AW3:AX3"/>
+    <mergeCell ref="BJ3:BJ4"/>
+    <mergeCell ref="BJ138:BK138"/>
+    <mergeCell ref="BA3:BB3"/>
+    <mergeCell ref="BC3:BD3"/>
+    <mergeCell ref="BE3:BF3"/>
+    <mergeCell ref="BG3:BG4"/>
+    <mergeCell ref="BH3:BH4"/>
+    <mergeCell ref="BI3:BI4"/>
+    <mergeCell ref="BI2:BJ2"/>
+    <mergeCell ref="BK2:BK4"/>
   </mergeCells>
   <conditionalFormatting sqref="BM5:BM138">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -27490,10 +27483,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA30D80-3AF2-4267-9155-DC45A47DFADD}">
   <dimension ref="A1:B46"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" style="235" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="235" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="235" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -27817,11 +27810,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F6D303D-967A-4DFE-B85F-262CEF014992}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" style="86" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" style="86" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="86"/>
+    <col min="1" max="1" width="19.44140625" style="86" customWidth="1"/>
+    <col min="2" max="2" width="22.109375" style="86" customWidth="1"/>
+    <col min="3" max="16384" width="9.109375" style="86"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
